--- a/xor.xlsx
+++ b/xor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tczplabu\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tczplabu\Documents\GitHub\xor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DF927F-C204-479D-B4D1-3873B97E36B2}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451944DF-FBDC-47FD-B03A-4B8553C88E8C}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13065" xr2:uid="{1F15999E-19BC-4BEE-96D9-16ED20FDFC1D}"/>
   </bookViews>
